--- a/Solutions/solution_models_HP98.xlsx
+++ b/Solutions/solution_models_HP98.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Thermolab\Github\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Thermolab\v_25_10_01\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8192A82D-8F50-46C3-B872-A7E16ABA3D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DD3ED5-862E-410D-9411-84ABBBE6B5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="16" activeTab="28" xr2:uid="{55A889F7-7CAF-4A87-AAEA-07BFCD9152AC}"/>
+    <workbookView xWindow="46680" yWindow="2355" windowWidth="28800" windowHeight="15435" firstSheet="2" activeTab="2" xr2:uid="{55A889F7-7CAF-4A87-AAEA-07BFCD9152AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Orthopyroxene" sheetId="1" r:id="rId1"/>
@@ -23,37 +23,38 @@
     <sheet name="Fluid-COH(DEW)" sheetId="29" r:id="rId8"/>
     <sheet name="Fluid-CO2-H2O" sheetId="20" r:id="rId9"/>
     <sheet name="Fluid-NaCl-H2O" sheetId="44" r:id="rId10"/>
-    <sheet name="Fluid-NaCl-KCl-H2O" sheetId="45" r:id="rId11"/>
-    <sheet name="test3" sheetId="51" r:id="rId12"/>
-    <sheet name="Fluid(F) (3)" sheetId="53" r:id="rId13"/>
-    <sheet name="Fluid(F) (4)" sheetId="54" r:id="rId14"/>
-    <sheet name="Fluid(F) (2)" sheetId="52" r:id="rId15"/>
-    <sheet name="Fluid(F)" sheetId="49" r:id="rId16"/>
-    <sheet name="aqFluid-NaCl-KCl-H2O" sheetId="46" r:id="rId17"/>
-    <sheet name="Melt" sheetId="5" r:id="rId18"/>
-    <sheet name="Salt(L)" sheetId="48" r:id="rId19"/>
-    <sheet name="Salt" sheetId="47" r:id="rId20"/>
-    <sheet name="Garnet" sheetId="3" r:id="rId21"/>
-    <sheet name="Clinopyroxene" sheetId="6" r:id="rId22"/>
-    <sheet name="Topaz" sheetId="50" r:id="rId23"/>
-    <sheet name="Spinel" sheetId="4" r:id="rId24"/>
-    <sheet name="Chlorite" sheetId="7" r:id="rId25"/>
-    <sheet name="Amphibole" sheetId="16" r:id="rId26"/>
-    <sheet name="Feldspar(C1)" sheetId="17" r:id="rId27"/>
-    <sheet name="Muscovite" sheetId="8" r:id="rId28"/>
-    <sheet name="Biotite" sheetId="9" r:id="rId29"/>
-    <sheet name="Staurolite" sheetId="10" r:id="rId30"/>
-    <sheet name="Chloritoid" sheetId="11" r:id="rId31"/>
-    <sheet name="Cordierite" sheetId="12" r:id="rId32"/>
-    <sheet name="Talc" sheetId="13" r:id="rId33"/>
-    <sheet name="Brucite" sheetId="15" r:id="rId34"/>
-    <sheet name="Antigorite" sheetId="14" r:id="rId35"/>
-    <sheet name="Magnesite" sheetId="18" r:id="rId36"/>
-    <sheet name="Dolomite" sheetId="21" r:id="rId37"/>
-    <sheet name="Melt(W07)" sheetId="19" r:id="rId38"/>
-    <sheet name="Epidote" sheetId="22" r:id="rId39"/>
-    <sheet name="Ilmenite" sheetId="23" r:id="rId40"/>
-    <sheet name="Carbonate" sheetId="43" r:id="rId41"/>
+    <sheet name="Plag(ideal)" sheetId="55" r:id="rId11"/>
+    <sheet name="Fluid-NaCl-KCl-H2O" sheetId="45" r:id="rId12"/>
+    <sheet name="test3" sheetId="51" r:id="rId13"/>
+    <sheet name="Fluid(F) (3)" sheetId="53" r:id="rId14"/>
+    <sheet name="Fluid(F) (4)" sheetId="54" r:id="rId15"/>
+    <sheet name="Fluid(F) (2)" sheetId="52" r:id="rId16"/>
+    <sheet name="Fluid(F)" sheetId="49" r:id="rId17"/>
+    <sheet name="aqFluid-NaCl-KCl-H2O" sheetId="46" r:id="rId18"/>
+    <sheet name="Melt" sheetId="5" r:id="rId19"/>
+    <sheet name="Salt(L)" sheetId="48" r:id="rId20"/>
+    <sheet name="Salt" sheetId="47" r:id="rId21"/>
+    <sheet name="Garnet" sheetId="3" r:id="rId22"/>
+    <sheet name="Clinopyroxene" sheetId="6" r:id="rId23"/>
+    <sheet name="Topaz" sheetId="50" r:id="rId24"/>
+    <sheet name="Spinel" sheetId="4" r:id="rId25"/>
+    <sheet name="Chlorite" sheetId="7" r:id="rId26"/>
+    <sheet name="Amphibole" sheetId="16" r:id="rId27"/>
+    <sheet name="Feldspar(C1)" sheetId="17" r:id="rId28"/>
+    <sheet name="Muscovite" sheetId="8" r:id="rId29"/>
+    <sheet name="Biotite" sheetId="9" r:id="rId30"/>
+    <sheet name="Staurolite" sheetId="10" r:id="rId31"/>
+    <sheet name="Chloritoid" sheetId="11" r:id="rId32"/>
+    <sheet name="Cordierite" sheetId="12" r:id="rId33"/>
+    <sheet name="Talc" sheetId="13" r:id="rId34"/>
+    <sheet name="Brucite" sheetId="15" r:id="rId35"/>
+    <sheet name="Antigorite" sheetId="14" r:id="rId36"/>
+    <sheet name="Magnesite" sheetId="18" r:id="rId37"/>
+    <sheet name="Dolomite" sheetId="21" r:id="rId38"/>
+    <sheet name="Melt(W07)" sheetId="19" r:id="rId39"/>
+    <sheet name="Epidote" sheetId="22" r:id="rId40"/>
+    <sheet name="Ilmenite" sheetId="23" r:id="rId41"/>
+    <sheet name="Carbonate" sheetId="43" r:id="rId42"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,12 +70,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="267">
   <si>
     <t>M1</t>
   </si>
@@ -874,6 +878,12 @@
   </si>
   <si>
     <t>HCl,aq,supcrt</t>
+  </si>
+  <si>
+    <t>ab,tc-ds55</t>
+  </si>
+  <si>
+    <t>an,tc-ds55</t>
   </si>
 </sst>
 </file>
@@ -1720,6 +1730,123 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3A5125-67CC-41F4-B904-31C9650F06BD}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C13">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10A6814-0771-42A0-ADD9-1E48210B747A}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1888,7 +2015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A12180A-F13E-4FE4-9A03-A2408796621E}">
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2631,7 +2758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{447866C9-83F2-4D54-B8B1-B7EDBAE001CE}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3191,7 +3318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF039772-33D1-4A90-B16C-EBCBA3F94116}">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3673,7 +3800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56CC1873-12A4-488D-9DD3-7EAD91BFEFD3}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4233,7 +4360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E257552C-6522-412B-AF95-E7CF0694A2DE}">
   <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5063,7 +5190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF3FA1E-0660-4E6A-9F40-CA62A83FBC49}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5224,7 +5351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A7D3560-73FF-4245-80DE-49DB35A6A3BB}">
   <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5766,175 +5893,6 @@
       <c r="E39">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89283236-4676-4076-9203-52B2B3A69DDB}">
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>227</v>
-      </c>
-      <c r="C4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>228</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14">
-        <f>1/100</f>
-        <v>0.01</v>
-      </c>
-      <c r="C14">
-        <f>1/100</f>
-        <v>0.01</v>
-      </c>
-      <c r="D14">
-        <f>1/100</f>
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6343,6 +6301,175 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89283236-4676-4076-9203-52B2B3A69DDB}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14">
+        <f>1/100</f>
+        <v>0.01</v>
+      </c>
+      <c r="C14">
+        <f>1/100</f>
+        <v>0.01</v>
+      </c>
+      <c r="D14">
+        <f>1/100</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DCDEFFC-BB9F-4104-B7A7-28EE9BF9EA78}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6479,7 +6606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33B391C-3BF6-4AAF-B42F-3471336276EC}">
   <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7045,7 +7172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8622EBC-6B59-41C1-A0B5-B72AB8142590}">
   <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8015,7 +8142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7592A47F-2013-4988-92AC-9BC6BD84AFA7}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8132,7 +8259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{925AD246-7441-4532-9250-4463A90017EB}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8282,7 +8409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0EC53B8-E4AC-4382-998D-57A5668183D5}">
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8738,7 +8865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161DBCB5-5176-4DC9-88DC-4D37E7E0DE9B}">
   <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9428,7 +9555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5DB00F-1DA4-4360-9CC7-4924D3BDF29C}">
   <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9810,7 +9937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D256944-9887-4D01-B486-8A5A88556D98}">
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10477,711 +10604,6 @@
       <c r="E39">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{107EBBF7-8126-4698-9154-55A6781978E0}">
-  <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>2</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>2</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-      <c r="J13">
-        <v>2</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
-      </c>
-      <c r="L13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="C17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="D17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="E17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="F17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="G17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="H17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="I17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="J17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="K17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="L17">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="1">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>12000</v>
-      </c>
-      <c r="D21" s="1">
-        <v>10000</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="1">
-        <v>12000</v>
-      </c>
-      <c r="C22" s="1">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1">
-        <v>3000</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="1">
-        <v>10000</v>
-      </c>
-      <c r="C23" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>7000</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="1">
-        <v>0</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="1">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="1">
-        <v>4000</v>
-      </c>
-      <c r="C26" s="1">
-        <v>8000</v>
-      </c>
-      <c r="D26" s="1">
-        <v>7000</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H28" s="1"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H36" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11329,6 +10751,711 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{107EBBF7-8126-4698-9154-55A6781978E0}">
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="D17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="E17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="F17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="G17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="H17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="I17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="J17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="K17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="L17">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="1">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>12000</v>
+      </c>
+      <c r="D21" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1">
+        <v>12000</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3000</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>7000</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4000</v>
+      </c>
+      <c r="C26" s="1">
+        <v>8000</v>
+      </c>
+      <c r="D26" s="1">
+        <v>7000</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H28" s="1"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D2FF73-BF3D-4FFA-991C-ADB00E1AEB98}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11545,7 +11672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43D4CC9-B60B-4FFB-8E97-63A544C61A1B}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11759,7 +11886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62433996-6A78-4C42-B701-F94A76CD98CF}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11997,7 +12124,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC5EA3B8-30F6-4ECC-A8AF-020A464756E5}">
   <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12298,7 +12425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1619535-04D6-4815-919C-E25105CD6D69}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12415,7 +12542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABEF32A7-DCB4-44DF-8E85-765EC52F830F}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12711,7 +12838,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1DDF854-756B-42A7-A515-A9979CF28555}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12864,7 +12991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AA2BDD3-56BF-46F4-A969-6F5E44BC336D}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13014,7 +13141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29BE789-FCEE-4419-8EA0-B9924A6B0C51}">
   <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14104,252 +14231,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA318424-9D96-4EC8-B79D-40733A02CEEE}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="C14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="D14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="E14">
-        <v>6.7000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>100</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>15400</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="2">
-        <v>15400</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>3000</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -14637,6 +14518,252 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA318424-9D96-4EC8-B79D-40733A02CEEE}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="C14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="D14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="E14">
+        <v>6.7000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>15400</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="2">
+        <v>15400</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3000</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C9EB150-1CC6-4D02-B1FA-7952EA79D5E4}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14996,7 +15123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B19F705E-B507-46E8-8605-FAA28F99A6BF}">
   <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
